--- a/etf_holdings/2026-08-28_common_holdings_all.xlsx
+++ b/etf_holdings/2026-08-28_common_holdings_all.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8.97%</t>
+          <t>8.94%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13.64%</t>
+          <t>13.48%</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>98.63%</t>
+          <t>98.44%</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8.97%</t>
+          <t>8.95%</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>3.69%</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -872,7 +872,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6.42%</t>
+          <t>6.01%</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>57.41%</t>
+          <t>56.60%</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>5.22%</t>
+          <t>5.15%</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4.84%</t>
+          <t>4.74%</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>48.01%</t>
+          <t>47.78%</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>4.36%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="AJ5" t="n">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>34.46%</t>
+          <t>34.57%</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="AJ6" t="n">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>23.70%</t>
+          <t>24.15%</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="U7" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="AJ7" t="n">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>16.83%</t>
+          <t>16.91%</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">

--- a/etf_holdings/2026-08-28_common_holdings_all.xlsx
+++ b/etf_holdings/2026-08-28_common_holdings_all.xlsx
@@ -634,11 +634,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9.87%</t>
+          <t>9.29%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11884000</v>
+        <v>11264000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11.74%</t>
+          <t>11.30%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4200000</v>
+        <v>4000000</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8.49%</t>
+          <t>8.43%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -686,11 +686,11 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>17.19%</t>
+          <t>16.02%</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>12000000</v>
+        <v>11100000</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.16%</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -738,7 +738,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="AD2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>98.44%</t>
+          <t>96.18%</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8.95%</t>
+          <t>8.74%</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.11%</t>
+          <t>8.99%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -820,7 +820,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8.93%</t>
+          <t>8.97%</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.24%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>5.85%</t>
+          <t>5.78%</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>3.91%</t>
+          <t>3.97%</t>
         </is>
       </c>
       <c r="AD3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>56.60%</t>
+          <t>56.47%</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>5.15%</t>
+          <t>5.13%</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -993,7 +993,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>4.65%</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -1019,11 +1019,11 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>6.62%</t>
+          <t>5.74%</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>872000</v>
+        <v>742000</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4.85%</t>
+          <t>5.01%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>6.23%</t>
+          <t>6.52%</t>
         </is>
       </c>
       <c r="AD4" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>47.78%</t>
+          <t>47.71%</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>4.75%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>5.13%</t>
+          <t>5.17%</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3.71%</t>
+          <t>3.83%</t>
         </is>
       </c>
       <c r="AD5" t="n">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>34.57%</t>
+          <t>34.92%</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4.29%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>4.70%</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="AD6" t="n">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>24.15%</t>
+          <t>23.53%</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.59%</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>16.91%</t>
+          <t>17.07%</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
